--- a/projects/Trade Area Modelling/Trade_Area_assignment.xlsx
+++ b/projects/Trade Area Modelling/Trade_Area_assignment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iolowoye\OneDrive - Deloitte (O365D)\Personal info\portfolio_website\projects\Trade Area Modelling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iolowoye\Portfolio\projects\Trade Area Modelling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF3E00F-48A5-47A1-BA20-8EFCD3239EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48852EC-A90E-48BE-8545-E26CAF894A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{88243168-CA61-7641-BD51-7CFBFCBA1015}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{88243168-CA61-7641-BD51-7CFBFCBA1015}"/>
   </bookViews>
   <sheets>
     <sheet name="Distance" sheetId="5" r:id="rId1"/>
